--- a/docs/cau-truc-du-lieu-ahs-phuc-tham.xlsx
+++ b/docs/cau-truc-du-lieu-ahs-phuc-tham.xlsx
@@ -31,28 +31,28 @@
     <sheet name="AHS_PHUCTHAM_BANAN_DIEU_CT" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AHS_VUAN'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AHS_VUAN_GIAIDOAN'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AHS_SOTHAM_CAOTRANG_DIEULUAT'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AHS_SOTHAM_BANAN_DIEU_CHITIET'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AHS_NGUOITHAMGIATOTUNG'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'AHS_NGUOITHAMGIATOTUNG_TUCACH'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AHS_FILE'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AHS_NGUOI_DAIDIEN'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'STPT_QUANLY_SOTHULY'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'LICHSU_XOA_SOTHULY'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AHS_THAMPHANGIAIQUYET'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'BAQD_CONGBO'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AHS_PHUCTHAM_THULY'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AHS_PHUCTHAM_BICANBICAO'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'AHS_PHUCTHAM_HDXX'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'AHS_PHUCTHAM_QUYETDINH_BICAN'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'AHS_SOTHAM_RUTKHANGCAO'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'AHS_SOTHAM_RUTKHANGNGHI'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'AHS_PHUCTHAM_QUYETDINH_VUAN'!$A$1:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'AHS_PHUCTHAM_BANAN'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'AHS_PHUCTHAM_BANAN_BICAO'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'AHS_PHUCTHAM_BANAN_DIEU_CT'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AHS_VUAN'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AHS_VUAN_GIAIDOAN'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AHS_SOTHAM_CAOTRANG_DIEULUAT'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AHS_SOTHAM_BANAN_DIEU_CHITIET'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AHS_NGUOITHAMGIATOTUNG'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'AHS_NGUOITHAMGIATOTUNG_TUCACH'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AHS_FILE'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AHS_NGUOI_DAIDIEN'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'STPT_QUANLY_SOTHULY'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'LICHSU_XOA_SOTHULY'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AHS_THAMPHANGIAIQUYET'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'BAQD_CONGBO'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AHS_PHUCTHAM_THULY'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AHS_PHUCTHAM_BICANBICAO'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'AHS_PHUCTHAM_HDXX'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'AHS_PHUCTHAM_QUYETDINH_BICAN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'AHS_SOTHAM_RUTKHANGCAO'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'AHS_SOTHAM_RUTKHANGNGHI'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'AHS_PHUCTHAM_QUYETDINH_VUAN'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'AHS_PHUCTHAM_BANAN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'AHS_PHUCTHAM_BANAN_BICAO'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'AHS_PHUCTHAM_BANAN_DIEU_CT'!$A$1:$H$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,16 +466,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,30 +487,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -523,37 +529,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Cap nhat giai doan phuc tham</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>MAGIAIDOAN</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Set MAGIAIDOAN=PHUCTHAM khi tao moi thụ lý</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>ENUM_GIAIDOANVUAN</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Code assignment</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>PHUCTHAM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -564,16 +575,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,30 +596,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -621,37 +638,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Ly do xoa thu ly PT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>PROC INSERT</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Ghi lich su khi xoa thu ly</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>LYDOXOATHULY/LYDOXOASOTHULY</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME; SP DM_DATAITEM_GETBYGROUPNAME</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Group theo lua chon xoa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -662,16 +684,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,30 +705,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -719,18 +747,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -740,26 +773,31 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Tham phan</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>CANBOID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO_GETBYDONVI_CHUCDANH THAMPHAN</t>
         </is>
@@ -773,26 +811,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Thu ky</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>THUKYID</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO Thu ky/TTV</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO_GetAllThuKy_TTV</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -802,26 +845,31 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Vai tro</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>MAVAITRO</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>VAITROTHAMPHAN</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME; SP DM_DATAITEM_GETBYGROUPNAME</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Default VTTP_GIAIQUYETPHUCTHAM; ddl disabled</t>
         </is>
@@ -835,26 +883,31 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Nguoi phan cong</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>NGUOIPHANCONGID</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO CA/PCA</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO_GETBYDONVI_2CHUCVU</t>
         </is>
@@ -868,18 +921,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>So quyet dinh</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>SOQD</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -889,18 +947,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Ngay quyet dinh</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>NGAYQD</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -910,18 +973,23 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Ngay phan cong</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>NGAYPHANCONG</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -931,18 +999,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Ngay nhan phan cong</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>NGAYNHANPHANCONG</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -952,18 +1025,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Ngay ket thuc</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>NGAYKETTHUC</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -973,37 +1051,42 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>File phan cong</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>dropThuLy only validation, not saved</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>AHS_FILE / DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>UploadFileID + DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>MABM=01-HS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1014,16 +1097,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,30 +1118,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -1071,33 +1160,38 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Cong bo ban an/quyet dinh PT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>PROC/ROW</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Insert/update cong bo khi dieu kien thoa</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>BAQD_CONGBO</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>DataExtensions Insert/Update</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1108,16 +1202,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1128,30 +1223,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -1165,18 +1265,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1186,26 +1291,31 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Toa an</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>TOAANID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>DM_TOAAN/Session</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Session DONVIID</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1215,26 +1325,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Nguoi ky</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>NGUOIKYID</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO_GETBYDONVI_THULY</t>
         </is>
@@ -1248,26 +1363,31 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Nguoi kiem ho so</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>NGUOIKIEMHOSOID</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO_GETBYDONVI</t>
         </is>
@@ -1281,18 +1401,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>So but luc</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>SOBUTLUC</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1302,30 +1427,35 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Truong hop thu ly</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>TRUONGHOPTHULY</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tra ID bang DM_DATAITEM.MA tru nhánh 998</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>DM_DATAITEM by MA / hardcoded 998</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>DM_DATAITEM lookup by MA; UI hardcoded values</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>998=Thu ly lai; MA AHS_PT_ThuLyKCKN/KC/KN</t>
         </is>
@@ -1339,26 +1469,31 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Noi dung thu ly XXL</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNGTLXXLAI</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNGTHULYXXL</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME; SP DM_DATAITEM_GETBYGROUPNAME</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2244=Khac</t>
         </is>
@@ -1372,22 +1507,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Ghi chu</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>GHICHUKHAC</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Khi noi dung=2244</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1397,22 +1537,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>So thu ly</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>SOTHULY</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>txtSoThuly ghi de to hop ddlSothuly+ddlStlPhu</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1422,26 +1567,31 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Toi danh chinh vu an</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>TOIDANHCHINH_VUAN</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>LINQ DM_BOLUAT_TOIDANH by vu an/bi can</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1451,18 +1601,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>Ngay thu ly</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>NGAYTHULY</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1472,22 +1627,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Den ngay</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>THOIHANDENNGAY</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mac dinh +15 ngay neu trong</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1497,26 +1657,31 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>Uy thac tu phap di</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>UTTPDI</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Checkbox hardcoded</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>CheckBox</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1/0</t>
         </is>
@@ -1530,29 +1695,34 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Thu tu</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>AHS_PHUCTHAM_THULY_GETMAXTT</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>AHS_PHUCTHAM_THULY_BL.GETNEWTT</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1563,16 +1733,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1583,30 +1754,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -1620,30 +1796,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Gan bi cao tham gia phuc tham</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>BICANID/VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Tao lien ket bi cao PT dua tren KC/KN</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>AHS_BICANBICAO/KCKN</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Code by AHS_SOTHAM_KHANGCAO/KHANGNGHI</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1653,37 +1834,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Tham gia phuc tham</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>BICANID/VUANID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Tick thi insert lien ket, bo tick thi remove</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>AHS_BICANBICAO</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>LoadGrid AHS_BICANBICAO_BL.GetAllByVuAnID</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Checkbox</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1694,16 +1880,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1714,30 +1901,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -1751,18 +1943,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1772,26 +1969,31 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Vai tro tham gia to tung</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>MAVAITRO</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded vai tro NTTT</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Hardcoded ListItem</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>THAMPHAN/HDXX/DUKHUYET/HTND/THUKY/KSV</t>
         </is>
@@ -1805,26 +2007,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Can bo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>CANBOID</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO/DM_CANBOVKS</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Theo vai tro</t>
         </is>
@@ -1838,26 +2045,31 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Nguoi phan cong</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>NGUOIPHANCONGID</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO CA/PCA</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>CA/PCA</t>
         </is>
@@ -1871,18 +2083,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Ngay phan cong</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>NGAYPHANCONG</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1892,18 +2109,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Ngay nhan phan cong</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>NGAYNHANPHANCONG</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1913,18 +2135,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>So quyet dinh</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>SOQD</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1934,18 +2161,23 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Ngay quyet dinh</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>NGAYQD</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1955,18 +2187,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Ngay ket thuc</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>NGAYKETTHUC</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1976,26 +2213,31 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>File bieu mau</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>AHS_FILE / DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>UploadFileID + DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MABM=01-HS/02-HS</t>
         </is>
@@ -2009,33 +2251,38 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>Cap nhat/thay doi NTTT BM03</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>ISTHAYDOI/CANBOID/SOQD/NGAYQD</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Clone/cap nhat HDXX khi QD 03-HS</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>DMCANBO_DUOCPC_BM03HS_PT / DMCANBO_NGUOIBITHAYDOI_TCTT_PT</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2046,16 +2293,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2066,30 +2314,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -2103,26 +2356,31 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Bi cao</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>BICANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>AHS_PHUCTHAM_BICANBICAO</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>AHS_PT_BiCao_GetAll</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2132,18 +2390,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2153,26 +2416,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Loai quyet dinh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>LOAIQDID</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_QD_LOAI</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>DM_QD_LOAI / DM_QD_QUYETDINH / DM_QD_QUYETDINH_LYDO via GSTPContext</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Loai bat tam giam by MA</t>
         </is>
@@ -2186,26 +2454,31 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Ten quyet dinh</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>QUYETDINHID</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>DM_QD_QUYETDINH</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>DM_QD_LOAI / DM_QD_QUYETDINH / DM_QD_QUYETDINH_LYDO via GSTPContext</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Filter phuc tham HS</t>
         </is>
@@ -2219,26 +2492,31 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Ly do</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>LYDOID</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>DM_QD_QUYETDINH_LYDO</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>DM_QD_LOAI / DM_QD_QUYETDINH / DM_QD_QUYETDINH_LYDO via GSTPContext</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>For 51-HS/52-HS</t>
         </is>
@@ -2252,22 +2530,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Noi giam giu</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>NOIGIAMGIU</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Bat tam giam</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2277,26 +2560,31 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Dieu luat ap dung them</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>DIEULUATAPDUNGTHEM</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded dieu luat</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>347/358</t>
         </is>
@@ -2310,22 +2598,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Bien ban nghi an ngay</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>BIENBANNGHIAN_NGAY</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>11-HS/12-HS</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2335,18 +2628,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>So quyet dinh</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>SOQUYETDINH</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2356,18 +2654,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Ngay quyet dinh</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>NGAYQD</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2377,18 +2680,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>Hieu luc tu</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>HIEULUCTU</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2398,18 +2706,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Hieu luc den</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>HIEULUCDEN</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2419,26 +2732,31 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>Nguoi ky</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>NGUOIKYID</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO CA/PCA/Chu toa</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>LoadNguoiKyDdlInfo</t>
         </is>
@@ -2452,26 +2770,31 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Tong hop hinh phat vu an khac</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>HINHPAT_VUAN_KHAC</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Checkbox hardcoded</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>CheckBox</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>1/0</t>
         </is>
@@ -2485,18 +2808,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>File upload</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNGFILE/TENFILE/KIEUFILE</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2506,33 +2834,38 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>File bieu mau</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>AHS_FILE / DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>UploadFileID + DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Template by QD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2543,16 +2876,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2563,30 +2897,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -2600,30 +2939,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Rut khang cao</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>KHANGCAOID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Writes depending IsKhangCao in grid</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>PKG_STPT_HS.AHS_PT_KCKN_TinhTrang_GETLIST</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>AHS_PHUCTHAM_BL.AHS_PT_KCKN_TinhTrang_GETLIST</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2633,18 +2977,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Ngay rut</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>NGAYRUT</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2654,26 +3003,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Tinh trang</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>TINHTRANG</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded tinh trang/cap</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx/code</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0/1/2 hardcoded</t>
         </is>
@@ -2687,18 +3041,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Noi dung</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNG</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2708,33 +3067,38 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Cap rut KN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>CAPRUTKN</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded tinh trang/cap</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx/code</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>CAPRUTKN=3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2745,16 +3109,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2765,30 +3130,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -2802,30 +3172,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Rut khang nghi</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>KHANGNGHIID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Writes depending IsKhangCao in grid</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>PKG_STPT_HS.AHS_PT_KCKN_TinhTrang_GETLIST</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>AHS_PHUCTHAM_BL.AHS_PT_KCKN_TinhTrang_GETLIST</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2835,18 +3210,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Ngay rut</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>NGAYRUT</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2856,26 +3236,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Tinh trang</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>TINHTRANG</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded tinh trang/cap</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx/code</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0/1/2 hardcoded</t>
         </is>
@@ -2889,18 +3274,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Noi dung</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNG</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2910,33 +3300,38 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Cap rut KN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>CAPRUTKN</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded tinh trang/cap</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx/code</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>CAPRUTKN=3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2947,16 +3342,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2967,30 +3363,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -3004,18 +3405,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3025,26 +3431,31 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Ten quyet dinh</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>QUYETDINHID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>DM_QUYETDINH_VUAN_PT</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>PKG_LOAD_DM_QDVUAN.AHS_DM_QUYETDINH_VUAN_PT</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3054,26 +3465,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Loai quyet dinh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>LOAIQDID</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_QD_QUYETDINH</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>DM_QD_LOAI / DM_QD_QUYETDINH / DM_QD_QUYETDINH_LYDO via GSTPContext</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Suy tu selected QD</t>
         </is>
@@ -3087,18 +3503,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Ngay mo phien toa</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>NGAYMOPT</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3108,18 +3529,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Dia diem mo phien toa</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>DIADIEMMOPT</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3129,26 +3555,31 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Hinh thuc xet xu</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>HINHTHUCXETXU</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded HTXX</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1..4</t>
         </is>
@@ -3162,26 +3593,31 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Ly do</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>LYDOID/LYDO_NAME</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>DM_QD_QUYETDINH_LYDO</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>DM_QD_LOAI / DM_QD_QUYETDINH / DM_QD_QUYETDINH_LYDO via GSTPContext</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>By QDID</t>
         </is>
@@ -3195,30 +3631,35 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Thay doi NTTT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>THAYDOITCTT</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>BM03</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded thay doi THTT</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>1=Tham phan;2=Hoi tham;3=Thu ky</t>
         </is>
@@ -3232,26 +3673,31 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Nguoi duoc phan cong</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>NGUOIDUOCPHANCONG</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>DMCANBO_DUOCPC_BM03HS_PT</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3261,26 +3707,31 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Nguoi bi thay</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>NGUOIBITHAY</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>DMCANBO_NGUOIBITHAYDOI_TCTT_PT</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3290,18 +3741,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>So quyet dinh</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>SOQUYETDINH</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3311,18 +3767,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Ngay quyet dinh</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>NGAYQD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3332,18 +3793,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>Hieu luc tu</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>HIEULUCTU</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3353,18 +3819,23 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Hieu luc den</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>HIEULUCDEN</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3374,26 +3845,31 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>Nguoi ky</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>NGUOIKYID</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO/manual</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>LoadNguoiKyDdlInfo/LoadNguoiKyTxtInfo</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3403,22 +3879,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>Chuc vu</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>CHUCVU</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Some QD IDs save selected ID as CHUCVU</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3428,18 +3909,23 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>File upload</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNGFILE/TENFILE/KIEUFILE</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3449,26 +3935,31 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>File bieu mau</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>AHS_FILE / DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>UploadFileID + DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>MABM = ma quyet dinh</t>
         </is>
@@ -3482,33 +3973,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Quyet dinh trong tab ban an</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>QUYETDINHID/SOQUYETDINH/NGAYQD/...</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Panel QD trong BanAn.aspx</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>DM_QUYETDINH_VUAN_PHUCTHAM_KETTHUC / DM_QD_QUYETDINH_LYDO</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>DM_QUYETDINH_VUAN_KETTHUC + DM_QD_QUYETDINH_LYDO</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3519,16 +4015,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3539,30 +4036,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -3576,37 +4078,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Giai doan phuc tham</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>PROC INSERT/UPDATE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Procedure PKG_STPT.GAIDOAN_IN_UP</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>PKG_STPT.GAIDOAN_IN_UP</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>GIAI_DOAN_BL</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Loai an=1, MAGIAIDOAN=PHUCTHAM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3617,16 +4124,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3637,30 +4145,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -3674,18 +4187,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3695,18 +4213,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Ngay mo phien toa</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>NGAYMOPHIENTOA</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3716,18 +4239,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Dia diem</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>DIADIEM</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3737,18 +4265,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>So ban an</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>SOBANAN</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3758,18 +4291,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Ngay ban an</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>NGAYBANAN</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3779,26 +4317,31 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Nguoi ky</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>NGUOIKY</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO/Chu toa</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Load nguoi ky/chủ tọa</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3808,26 +4351,31 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Ket qua phuc tham</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>KETQUAPHUCTHAMID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>DM_KETQUA_PHUCTHAM</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>GSTPContext DM_KETQUA_PHUCTHAM</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>ISAHS=1, ISBANAN=1</t>
         </is>
@@ -3841,26 +4389,31 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Ly do ban an</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>LYDOBANANID</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>DM_KETQUA_PHUCTHAM_LYDO</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>DM_KETQUA_PT_LYDO_GETLIST</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3870,26 +4423,31 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Toi danh chinh vu an</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>TOIDANHCHINH_VUAN</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>LoadListToiDanh_ByVuAnId</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3899,26 +4457,31 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Cong bo ban an</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>ISCONGBOBA</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded yes/no</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
@@ -3932,18 +4495,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>File ban an</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>NOIDUNGFILE/TENFILE/KIEUFILE</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3953,26 +4521,31 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>File bieu mau 28-HS</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>AHS_FILE / DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>UploadFileID + DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>MABM=28-HS</t>
         </is>
@@ -3986,26 +4559,31 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>An le</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>ISANLE/SOANLE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Danh sach an le</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>CONGBO_BL.DBLINK_GET_LIST_ANLE</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4015,26 +4593,31 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>An rut gon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>ISANRUTGON</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded yes/no</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
@@ -4048,26 +4631,31 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>Bao luc gia dinh</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>ISBAOLUCGIADINH</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded yes/no</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
@@ -4081,33 +4669,38 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>Xet xu luu dong</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>ISXXLUUDONG</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded yes/no</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4118,16 +4711,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4138,30 +4732,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -4175,18 +4774,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Ban an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>BANANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4196,18 +4800,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Bi cao</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>BICAOID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4217,18 +4826,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Tham gia phien toa</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>ISTHAMGIAPHIENTOA</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4238,18 +4852,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>An phi</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>ANPHI</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4259,21 +4878,26 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Ngay nhan ban an</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>NGAYNHANBANAN</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4284,16 +4908,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4304,30 +4929,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -4341,26 +4971,31 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Ban an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>BANANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Copy/sync dieu luat/toi danh</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4370,26 +5005,31 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Bi can</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>BICANID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Copy/sync dieu luat/toi danh</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4399,33 +5039,38 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Dieu luat/toi danh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>DIEULUATID/TOIDANHID/TENTOIDANH</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Copy/sync dieu luat/toi danh</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Copy/sync dieu luat/toi danh</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4436,16 +5081,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4456,30 +5102,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -4493,33 +5144,38 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Chon toi danh chinh PT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>ISMAIN_THULYPT</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Fallback cap nhat tren cao trang dieu luat</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Popup/list toi danh</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4530,16 +5186,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4550,30 +5207,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -4587,33 +5249,38 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Chon toi danh chinh PT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>ISMAIN_THULYPT</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Cap nhat ISMAIN_THULYPT tren dieu chi tiet ban an so tham</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>DM_BOLUAT_TOIDANH</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Popup/list toi danh</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4624,16 +5291,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4644,30 +5312,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -4681,18 +5354,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Vu an</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VUANID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4702,18 +5380,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Ho ten / Ten co quan</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>HOTEN</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4723,18 +5406,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Dia chi chi tiet</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>DIACHICHITIET</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4744,26 +5432,31 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Doi tuong</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>LOAIDT</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded doi tuong TGTT</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0=Ca nhan;1=Co quan;2=To chuc</t>
         </is>
@@ -4777,18 +5470,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Ngay sinh</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>NGAYSINH</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4798,18 +5496,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Nam sinh</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>NAMSINH</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4819,26 +5522,31 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Gioi tinh</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>GIOITINH</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded gioi tinh</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1=Nam;0=Nu</t>
         </is>
@@ -4852,26 +5560,31 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Nghe nghiep</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>NGHENGHIEPID</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>NGHENGHIEP</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME; SP DM_DATAITEM_GETBYGROUPNAME</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>ENUM_DANHMUC.NGHENGHIEP</t>
         </is>
@@ -4885,18 +5598,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Ngay tham gia</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>NGAYTHAMGIA</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4906,18 +5624,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Nguoi dai dien</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>NDD_HOTEN</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4927,18 +5650,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>Chuc vu NDD</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>NDD_CHUCVU</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4948,18 +5676,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>CMND NDD</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>NDD_CMND</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4969,18 +5702,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>Dien thoai NDD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>NDD_MOBILE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4990,18 +5728,23 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Email NDD</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>NDD_EMAIL</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5011,26 +5754,31 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>Tre vi thanh nien</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>ISTREVITHANHNIEN</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded yes/no</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0=Khong;1=Co</t>
         </is>
@@ -5044,26 +5792,31 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>Phan loai do tuoi</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>LOAITREVITHANHNIEN</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded phan loai tuoi</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Hardcoded in aspx</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1..4</t>
         </is>
@@ -5077,26 +5830,31 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>Is phuc tham</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>ISPHUCTHAM</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Hardcoded fixed</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Code assignment</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>ISPHUCTHAM=1</t>
         </is>
@@ -5110,18 +5868,23 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>Ten VPLS</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>TEN_VPLS</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5131,18 +5894,23 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Doan LS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>DOAN_LS</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5152,26 +5920,31 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>Nguoi phan cong</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>NGUOIPHANCONGID</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>DM_CANBO</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO via DM_CANBO_BL / DM_CANBOVKS_BL</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>DM_CANBO_GETBYDONVI_3CHUCVU</t>
         </is>
@@ -5185,18 +5958,23 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>So dang ky</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>SO_DK</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5206,18 +5984,23 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>Ngay dang ky</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>NGAY_DK</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5227,21 +6010,26 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>Dien thoai LS/NDD</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>NDD_MOBILE</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G24"/>
+  <autoFilter ref="A1:H24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5252,16 +6040,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5272,30 +6061,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -5309,37 +6103,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Tu cach tham gia</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>TUCACHID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>FK NGUOIID -&gt; AHS_NGUOITHAMGIATOTUNG.ID</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>TUCACHTGTTHS</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME; SP DM_DATAITEM_GETBYGROUPNAME</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>ENUM_DANHMUC.TUCACHTGTTHS; filter out BICANDAUVU/BICAN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5350,16 +6149,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5370,30 +6170,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -5407,30 +6212,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>File phan cong PT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Ghi AHS_FILE va gan FILEID vao AHS_THAMPHANGIAIQUYET</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>GSTPContext DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>MABM=01-HS; MAGIAIDOAN=PHUCTHAM</t>
         </is>
@@ -5444,30 +6254,35 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>File NTTT phuc tham</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Ghi AHS_FILE va gan FILEID vao AHS_PHUCTHAM_HDXX</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>GSTPContext DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>MABM=01-HS/02-HS</t>
         </is>
@@ -5481,30 +6296,35 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>File quyet dinh bi can/bi cao PT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Ghi AHS_FILE va gan FILEID vao AHS_PHUCTHAM_QUYETDINH_BICAN</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>GSTPContext DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Template selected QD</t>
         </is>
@@ -5518,30 +6338,35 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>File quyet dinh vu an PT</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Ghi AHS_FILE va gan FILEID vao AHS_PHUCTHAM_QUYETDINH_VUAN</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>GSTPContext DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>MABM = ma quyet dinh</t>
         </is>
@@ -5555,37 +6380,42 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>File ban an phuc tham</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>FILEID</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Ghi AHS_FILE va gan FILEID vao AHS_PHUCTHAM_BANAN</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>GSTPContext DM_BIEUMAU</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>MABM=28-HS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5596,16 +6426,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5616,30 +6447,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -5653,33 +6489,38 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Dai dien cho bi cao/bi hai</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>PROC INSERT/UPDATE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Procedure ghi quan he dai dien</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>AHS_PHUCTHAM_BICANBICAO/BiHai</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>GetAllBiCan_bihai_PhucTham</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5690,16 +6531,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5710,30 +6552,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Lookup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lookup Name/Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lookup Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hardcoded/Filter Values</t>
         </is>
@@ -5747,37 +6594,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Cap nhat quan ly so thu ly PT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>PROC UPDATE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Params hardcoded 3,1 trong code</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>PKG_STPT_QUANLY_SOTHULY</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Oracle package</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>update_STPT_QUANLY_SOTHULY(3,1,...)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>